--- a/sample.xlsx
+++ b/sample.xlsx
@@ -1,23 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30305"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hk991\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF56618-58FC-4EF9-ABD9-76DAABF8355B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C483E3CB-3B8E-469C-A0A6-4C84557F7825}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{290FEC64-555D-4CD4-BA13-A39EB70AEFAA}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$5:$K$7</definedName>
-  </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,12 +26,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>1 for Low
 2 For Medium
@@ -79,14 +74,12 @@
     <t>solution</t>
   </si>
   <si>
-    <t>KCGSMFSACFSAA0001</t>
-  </si>
-  <si>
-    <t>&lt;body&gt;
-&lt;p&gt;
+    <t>TESTAUTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 Bonds payable would generally be represented as a percentage of which of the following options in a common-size statement?
-&lt;/p&gt;
-&lt;/body&gt;</t>
+</t>
   </si>
   <si>
     <t>Long-term assets</t>
@@ -101,20 +94,9 @@
     <t>Total stockholders' equity</t>
   </si>
   <si>
-    <t>&lt;p&gt;In a common-size balance sheet, every item is expressed as a percentage of total assets or equivalently, total liabilities and stockholders’ equity (since both sides of the balance sheet are equal).&lt;/p&gt; &lt;p&gt;Bonds payable is a long-term liability, meaning it falls under the liabilities section of the balance sheet.&lt;/p&gt; &lt;p&gt;Therefore, to maintain consistency in comparison, bonds payable is expressed as a percentage of the total liabilities and stockholders' equity.&lt;/p&gt;</t>
-  </si>
-  <si>
-    <t>KCGSMFSACFSAA0002</t>
-  </si>
-  <si>
-    <t>&lt;body&gt;
-  &lt;p&gt;
-    Michael's accounts receivable (AR) increased from $239 to $684 from 20X1 to 20X2. If we designate 20X1 as the base year with a value of 1.00, determine the increase in AR for 20X2.
-  &lt;/p&gt;
-&lt;/body&gt;</t>
-  </si>
-  <si>
-    <t xml:space="preserve">&lt;p&gt;When using index analysis with a base year, it measures how much a value has changed relative to that base year. The base year is assigned an index value of 1.00, and subsequent years are expressed as multiples of that base.&lt;/p&gt; &lt;p&gt;1: Calculate the 20X2 Index Value&lt;/p&gt; &lt;p&gt;Formula: Index = (Current Year Value ÷ Base Year Value) × Base Index&lt;/p&gt; &lt;p&gt;Index for 20X2 = ($684 ÷ $239) × 1.00&lt;/p&gt; &lt;p&gt;Index for 20X2 = 2.862&lt;/p&gt; &lt;p&gt;2: Determine the Increase&lt;/p&gt; &lt;p&gt;For the "increase" in AR for 20X2&lt;/p&gt; &lt;p&gt;Since 20X1 (base year) = 1.00&lt;/p&gt; &lt;p&gt;Increase = 20X2 Index - Base Year Index&lt;/p&gt; &lt;p&gt;Increase = 2.862 - 1.00 = 1.862&lt;/p&gt; </t>
+    <t>n a common-size balance sheet, every item is expressed as a percentage of total assets or equivalently, total liabilities and stockholders’ equity (since both sides of the balance sheet are equal).
+Bonds payable is a long-term liability, meaning it falls under the liabilities section of the balance sheet.herefore, 
+to maintain consistency in comparison, bonds payable is expressed as a percentage of the total liabilities and stockholders' equity.</t>
   </si>
 </sst>
 </file>
@@ -131,6 +113,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -139,12 +127,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -196,71 +178,42 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -568,73 +521,85 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30BC9E27-BAAF-41AF-90B6-94E594BF3F8A}">
-  <dimension ref="A4:K7"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="63.42578125" customWidth="1"/>
-    <col min="6" max="6" width="37.42578125" customWidth="1"/>
-    <col min="7" max="8" width="37.42578125" style="8" customWidth="1"/>
-    <col min="9" max="9" width="37.42578125" customWidth="1"/>
-    <col min="11" max="11" width="63.42578125" customWidth="1"/>
+    <col min="1" max="4" width="9.140625" style="8"/>
+    <col min="5" max="5" width="32.85546875" style="8" customWidth="1"/>
+    <col min="6" max="10" width="9.140625" style="8"/>
+    <col min="11" max="11" width="45.5703125" style="8" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:11" ht="43.15">
+    <row r="1" spans="1:11">
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+    </row>
+    <row r="4" spans="1:11" ht="76.5">
       <c r="D4" s="10" t="s">
         <v>0</v>
       </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" t="s">
+      <c r="A5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="100.9">
+    <row r="6" spans="1:11" ht="183">
       <c r="A6" s="1">
-        <v>9</v>
-      </c>
-      <c r="B6" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="3">
         <v>0.56999999999999995</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="2">
         <v>2</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -643,64 +608,37 @@
       <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="5" t="s">
         <v>16</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="4">
         <v>3</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="129.6">
-      <c r="A7" s="1">
-        <v>9</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="6">
-        <v>0.61</v>
-      </c>
-      <c r="D7" s="4">
-        <v>2</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1.31</v>
-      </c>
-      <c r="G7" s="3">
-        <v>2.65</v>
-      </c>
-      <c r="H7" s="7">
-        <v>1.86</v>
-      </c>
-      <c r="I7" s="3">
-        <v>2</v>
-      </c>
-      <c r="J7" s="5">
-        <v>3</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>21</v>
-      </c>
+    <row r="7" spans="1:11">
+      <c r="A7" s="1"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:K7" xr:uid="{30BC9E27-BAAF-41AF-90B6-94E594BF3F8A}"/>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="duplicateValues" dxfId="0" priority="10" stopIfTrue="1"/>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>